--- a/spider/cnew_data.xlsx
+++ b/spider/cnew_data.xlsx
@@ -1,42 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="16155" windowHeight="8505"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -52,30 +44,88 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -149,7 +199,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -184,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -360,34 +408,493 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>财经</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>中国—东盟非遗集中亮相南宁 促文明互鉴</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+南宁4月1日电 (黄艳梅 张广权)中国侗族大歌、越南北宁官贺民歌、马来西亚传统舞蹈……4月1日，来自中国与东盟国家的非物质文化遗产代表性项目集中亮相广西南宁市，为民众呈现一场精彩纷呈的文化盛宴。
+　　第三届中国—东盟非物质文化遗产周当日在南宁启幕。此次活动以“山水相连 文明互鉴”为主题，聚焦非遗传承保护与创新发展，汇聚中国与东盟国家非遗瑰宝，涵盖传统音乐、舞蹈、戏曲、手工艺等领域，打造中国—东盟文化交流合作新平台。
+　　在南宁民歌湖景区，舞蹈秀《壮美之约》、朝鲜族长鼓舞《长鼓情》、傣族象脚鼓舞《新农村的鼓声》、广东英歌舞《中华战舞 英歌雄风》等节目集中展演。来自东盟国家以及中国多个省(区、市)的非物质文化遗产代表性项目在街区巡游，吸引民众观赏。
+　　在非遗集市上，中国四大名锦华美登场；南宁老友粉、越南鸡肉粉等20余种米粉让民众体验“嗦粉狂欢”；民众还可以品茶香、赏名陶，体验越南竹编、老挝织布、印尼传统乐器等异域风情。
+　　本届非遗周还推出中国—东盟戏曲文化交流主题展、中国—东盟非遗交流会、邕剧主题展、“大师来了”非遗大讲堂等。
+　　马来西亚纯粹舞团当天带来舞蹈作品《KURIK KUNDI》。据舞团艺术总监谢凯贤介绍，该作品融合了马来西亚各地民间舞蹈元素，舞蹈音乐也融合了马来西亚不同地区的方言，具有浓厚的本土文化特色。
+　　“非遗架起了一座交流桥梁。在这个国际性舞台上，让我们有机会了解和学习各国艺术家在舞蹈、歌唱、表演等方面的技巧和各国优秀传统文化。今后有机会我还想来中国进行文化交流。”马来西亚舞蹈演员赵健扬接受
+采访时说。(完)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>https://www.chinanews.com.cn/cj/2025/04-01/10393111.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>社会</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>有得花、有得耍、有得吃，“三月三”展新颜！多彩民俗焕发澎湃活力</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>央视网消息：又是春来“三月三”，山歌起、绣球飞。广西、江西、贵州等地纷纷举办丰富多彩且极具特色的民俗活动，共赴一场民俗文化之约。
+　　农历三月初三，俗称“三月三”，在广西又被叫作“歌圩节”。这一天，壮族、瑶族、侗族、苗族等多民族群众穿上节日盛装欢庆节日。
+　　南宁民歌湖的民歌广场是2025年广西“三月三”的主会场。在水上主舞台表演的是来自全国各地“四季村歌”歌队的十几个代表队。2025年的广西“三月三”主会场还有很多有意思的设置。比如，“有得花”鲜花市集、“有得耍”科技潮玩市集、“有得吃”东南亚风情水上市集等。
+　　在玉林市玉州区鹏垌村，广场的竹竿迎客舞吸引不少游客互动。非遗展区内还展示了手工香囊、版画、漆扇等传统手工艺，游客们纷纷驻足欣赏并参与体验，感受传统文化的魅力。
+　　农历“三月三”也是畲族人民重要的传统节日。在赣州会昌县洞头乡洞头畲族村，当地畲族群众托举“九龙九凤”沿街祈福巡游。“九龙九凤”承载着畲族群众对风调雨顺、五谷丰登、阖家幸福的祈愿。
+　　农历“三月三”也是贵州布依族群众的传统节日。在黔西南的陂鼐古寨，当地村民和游客一起品尝美食、欣赏非遗展演。
+　　在云南曲靖市师宗县，当地举办了以“篝火狂欢夜”“泼水祈新福”为核心亮点的特色活动，融合多元内容，让游客沉浸感受壮乡文化的澎湃活力，让“三月三”这个古老的节日焕发出新的活力。
+　　在湖北阳新县，一年一度的富池“三月三”庙会吸引人们出门踏青、祈福纳吉。广场上，十多米高的青竹上悬挂着上百个彩球，红球绿球寓意添丁、黄球寓意得财、蓝球寓意平安。青竹被放倒后，众人争相跳跃抢摘彩球，气氛十分火热。</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.chinanews.com.cn/sh/2025/04-01/10393112.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>湾区</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>十月稻田斩获5项iSEE全球奖，玉米品类创新引爆消费热潮</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025年3月30日，第七届iSEE全球奖颁奖典礼在上海国家会展中心拉开帷幕。本届颁奖典礼现场聚焦食品领域创新与美味，作为家庭食品创新品牌的十月稻田一次性斩获5项iSEE全球奖，以玉米品类创新案例获得“iSEE全球食品创新奖(企业类)”，旗下寒露秋香长粒香米、黄糯玉米等4款产品摘星“iSEE全球美味奖”。
+　　iSEE全球奖参与案例累计10000+，覆盖中国、日韩、欧洲、北美、澳洲等国家与地区。十月稻田连续两年在众多国际国内品牌中突围，赢得多项iSEE全球奖，不仅体现了“中国味香香香”的全球魅力，也更加印证了十月稻田在品类创新上的敏锐洞察力。
+　　近年，随着健康粗粮、优质碳水理念的兴起，玉米正在成为人们在米面之外的主食新宠。十月稻田敏锐捕捉这一新趋势，将玉米打造成轻食、零食化产品，目前已推出玉米棒、玉米段、玉米粒，以及黄糯玉米、白糯玉米、鲜食水果玉米等30多款玉米产品。十月稻田打破人们对玉米“传统主食”的认知，让玉米以多元、快消品的形态出现，满足了不同消费群体的多样化需求。
+　　事实上，十月稻田自成立之日起，始终在求新、求变。抓住互联网的发展红利，迅速与各大电商平台建立合作，一举打开农产品线上热销的突破口，实现了高速发展。随着中国零售变革加速，十月稻田近年来积极布局高势能渠道，并且加快全域营销的布局。目前已布局京东、拼多多等30余个大型电商平台，并做到多个单品电商销售排名第一。同时，全面启动线下经销商全国招商，与近百家现代商超渠道达成合作，还积极拓展社交电商平台、社区团购平台等新兴渠道的合作机会，持续深化全渠道布局。
+　　在营销上，十月稻田也在积极探索更多的品牌输出形式，以创始人IP为输出载体，在“十月稻田兵哥”、“十月稻田君姐”的视角下，将种植基地、超级工厂、产品加工生产等各个流程生动真实地呈现在大众面前。2025年初还跟《新白娘子传奇》IP联合，和“小香风轻盈推荐官”赵雅芝一起，掀起了一场轻食季玉米真香风潮。随着IP影响力的不断扩大，十月稻田的增长势能愈发强劲，同时一个可信赖、有温度的品牌形象愈发深入人心。
+　　数据显示，十月稻田玉米连续两年火遍全网。截至2025年3月，抖音平台仅十月稻田黄糯玉米单品链接累计销量就超过1300万单；玉米品类全国销量领先；2024年业绩报告中，玉米产品营收8.15亿元，占比由2023年的2.7%提升至14.2%，增长势头强劲。玉米，已成十月稻田第二增长引擎。
+　　十月稻田，依托东北得天独厚的生态环境、优质的土壤条件，从源头把控品质。东北的肥沃黑土400年才形成1厘米，有机质含量高，加上当地昼夜温差大，农作物一年只收获一季，这里孕育出的农产品，口感和品质无可比拟。十月稻田通过东北及内蒙粮食核心产区布局，将高品质的产品送到消费者的餐桌，一直致力于为14亿国人的一日三餐服务。
+　　原产地布局的同时，十月稻田持续加码全链路一体化建设。一方面，斥巨资在5大生产基地附近设立现代化工厂、建上万平仓储车间、添先进设备；另一方面，在全国范围建立5大自营区域中心仓，以及10个地方仓库。从田间地头到消费者餐桌，十月稻田搭建了一套现代化库配体系，保障消费者对安全、健康、美味家庭食品的需求，提升用户体验。
+　　基于源头严控品质的严谨态度，又有全链路一体化的保驾护航，十月稻田对初级农产品进行了一场全链路现代化改造，实现了从田间地头进入工厂，再走上消费者餐桌的品牌化蜕变。本次iSEE全球奖，十月稻田寒露秋香长粒香米、黄糯玉米斩获二星认证，十月稻田鲜食黄糯玉米、柴火大院五常大米摘得三星“iSEE全球美味奖”。
+　　在日常食用场景中越来越普遍的玉米，正在迎来新风口。今年两会期间，国家提出“体重管理年”行动，人们对健康食品的需求也水涨船高。中国食品工业协会《玉米主食化趋势白皮书》调查数据显示，约90%的受访者会选择玉米，预计2025年主食玉米市场规模将达到5.77千亿元。此背景下，健康美味、品质稳定、有品牌保障的玉米产品，未来潜力巨大足以预见。
+　　十月稻田对农产品的品牌化运营战略，已经得到了市场的阶段性验证，其在玉米品类上的成功，也为行业提供了新的解题思路——以农产品品牌为起点，构建新型产业链，从而塑造现代农业的系统影响力。据了解，十月稻田未来还会将创新延伸到更多品类之上。
+　　粮食产业关乎民生，十月稻田一头连接着中国农民的“钱袋子”，一头连接着厨房食品的“菜篮子”，持续为消费者提供优质的产品和服务。在国家政策东风与万亿健康食品市场的双重驱动下，十月稻田的美味还将加速蔓延开来。</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.chinanews.com.cn/dwq/2025/04-01/10393107.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>财经</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>建造“好房子” 打造民生大幸福</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2025年，“好房子”首次被写入政府工作报告，同时也成为社会关注的热点话题。什么样的房子才是“好房子”？建“好房子”，需要从哪些方面着手？未来，“好房子”还会有怎样的形态？多位建筑设计领域的专家、学者接受《中国新闻》报采访，各自给出答案。
+　　“政府工作报告提出，要完善标准规范，推动建设‘安全、舒适、绿色、智慧’的‘好房子’。”在今年的全国两会期间，住房和城乡建设部(以下简称“住建部”)部长倪虹提及“好房子”建设指南中的一项内容——住宅层高提高到不低于3米。
+　　此前遵照的层高标准是2011年颁布的《住宅设计规范》，其中明确规定“住宅层高宜为2.8米。”在九三学社社员、海淀区政协委员、海淀区建筑行业协会会长张轲看来，房子“长高”20厘米，就是从“有”到“优”的证明。
+　　他解释道，在建筑测算上，常规的卧室在9平方米左右，假设一个人待在家中关闭门窗休息的时间为11—12小时，需要的空气消耗量在27立方米以上。因此，层高提高20厘米，更贴近人体需求，同时“造价也并不会线性递增”。
+　　除了关注“高度”，“好房子”的标准涉及居民生活的方方面面。住建部公布的《城市住房发展规划和年度计划编制导则(试行)》(以下简称“《导则》”)中提到，“满足居民对住房设计、设施配置、环境空间、物业服务、通勤效率等方面的多维度品质需求，建设安全、舒适、绿色、智慧的‘好房子’。”
+　　“从‘住有所居’到‘住有优居’，其实解决的是从量到质的居住需求变化。”中央美术学院建筑学院教授、民盟北京市委会第十三届委员会委员何崴表示，“好房子”的提法既符合国家高质量发展的方向，也回应了居民对美好居住条件的诉求。
+　　在全国两会记者会上，倪虹为“好房子”的落地“划重点”——一方面，结合新技术、新工艺、新材料、新产品把新房子建成“好房子”；另一方面，结合城市更新，把老房子改成“好房子”。
+　　记者梳理发现，目前，全国半数以上省份相继推进“好房子”住房标准建设、示范项目试点等举措。多家商业地产百强企业加大对“好房子”的建设投入。
+　　在北京市昌平区沙河镇，“好房子”的样貌得以具象化。3月初，沙河镇中关村生命科学园的一个小区内，“风雨连廊”联通各单元楼，楼房首层被打造为共享书房、茶水间、健身房、儿童活动室等不同场所，未来，成为居民们休闲娱乐的好去处。
+　　这是全国“好房子”设计大赛首个落地示范项目。将首层打造为公共区域、室内设计开敞式阳台，住户能活动的室内外范围更大，同时这部分空间不计入住宅面积，换言之，住户实际使用的面积更大了。
+　　合理利用底层架空空间、鼓励在多层空间设置开敞式阳台、打造风雨连廊、增配邻里共享公共空间……这些创新举措在去年11月底印发的《北京市高品质商品住宅设计导则(试行)》中被首次提出，并在今年2月初发布的《北京市平原多点地区“好房子”规划管理相关技术要点(试行)》中进一步细化。这也是平原地区建设“好房子”的示范性标准，将形成可复制的经验进行推广。
+　　除了打造公共区域外，不少传统房企在技术和服务上也有所迭代。比如，传统房企与科技型企业合作开发新一代“全屋智能家居系统”，该系统通过联动智能传感器及使用语音、App等智能交互技术，可以为住户打造出聚会、睡眠等多个生活场景，并进行空气检测等。
+　　此外，房企还推出了不少新户型，比如借助模块化家具、可移动墙体等技术打造的可变空间户型；融入垂直绿化、公共空间和智能技术的第四代住宅等等。房地产研究机构克而瑞公布的数据显示，在2024年房企销售业绩TOP100榜单中，多家房企推出“‘好房子’建设技术标准”，今年年初，第四代住宅在南京等地位列销售榜前列。
+　　在此前的记者会上，住建部还表示，把2000年以前建成的城市老旧小区都纳入城市更新改造范围。
+　　“我国是世界上既有住房最多的国家，预计2040年前后，近80%的住房将进入设计使用年限的中后期。”全国政协委员、民建中央法制委员会委员罗卫表示。
+　　在老旧小区的“体检”中，常见的问题包括屋顶漏水、隔音效果差等质量问题。此外，罗卫在调研中发现，住房建设、买卖、租赁、运营、维修、拆除等环节管理衔接不足，服务链条脱节，加速了房屋的老化。
+　　为此，她建议将住房涉及的上述环节作为一个全生命周期来统筹管理和发展服务。加快制定住房全生命周期管理相关政策法规，特别是住房体检制度、住房养老金制度、住房保险制度等住房全生命周期安全管理制度，为住房提供更多基础保障。目前，建立健全房屋全生命周期安全管理制度已被写入《导则》，作为重点任务推进。
+　　房屋维修牵扯出更多问题：谁负责维修？资金从何而来？维修的标准是什么？张轲表示，房屋的管理应由产权人负责，住房涉及多个业主，进行改动需要业主同意并以公维基金作为资金来源，但目前公维基金收缴情况欠佳。
+　　针对上述问题，政府、社区、企业一齐发力解决问题。在资金方面，建立“政府引导、居民自筹、社会参与”的多元化资金筹措模式；在标准制定方面，住建部请建筑行业领域多位专家牵头，对老旧小区电梯改造、保温加固等多项问题进行调研并制定标准；此外，多地社区也以“大家商量着办”的方式，让居民们一吐为快，就改造方案形成共识。
+　　“好房子”的设计理念关键在于以人为本，这是多位受访者的共识。
+　　“‘好房子’离不开科技的赋能。科技将重构‘住’的本质，让房子不再是钢筋水泥的堆砌，而是会呼吸、能思考、懂关怀的数字生命体。”谈及自己心目中的“好房子”，罗卫说。
+　　张轲举例道，对于独自居家的老人而言，房屋有如拐杖，未来可以在房屋产权人同意的前提下安置室内智能感应系统，通过监测老年人的活动空间和停留时长观察其身体状态，联动社区实施应急送医机制。智能家具的安置也将为很多行动不便的老人减轻诸如难以弯腰、爬高的负担。
+　　房地产专业人士表示，数字技术的创新应用也将拓展到房屋的设计、装修、运营、维护等全链条。比如，可以利用建筑信息模型、AI等技术支持用户参与房屋定制，降低后期改造成本；并通过VR/AR技术实现“所见即所得”的购房、装修体验，减少决策误差。
+　　绿色环保目标也使得更多新材料有了用武之地。房地产专业人士提到，可以使用裂缝自愈涂层等自修复材料延长建筑生命周期；使用钢结构＋再生塑料复合板材，实现房屋“拆解＋重组”循环利用。(完)(《中国新闻》报 宋珂欣 报道)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.chinanews.com.cn/cj/2025/04-01/10393106.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>国际</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>L3级私家车上路 事故谁担责？</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+　　广州日报讯 (全媒体记者 邓莉)从今天起，北京将率先允许L3级以上的自动驾驶私家车上路。根据4月1日正式实施的《北京市自动驾驶汽车条例》(以下简称《条例》)，L3级及以上智驾级别的应用场景新增了“个人乘用车出行”，为普通车主敞开了“大门”，同时《条例》也对自动驾驶汽车发生事故后责任如何认定进行了相关规定。
+　　在近日举办的中国电动汽车百人会论坛(2025)上，工信部相关人士同时明确：将有条件批准L3级自动驾驶车型生产准入。为此，该《条例》的实施被视为自动驾驶行业的重要分水岭。今年以来，汽车主机厂积极加速高阶智驾平权，尤其面向私家车市场的L3级乘用车量产落地成为焦点。
+　　自动驾驶事故责任划分有了参考答案？
+　　按照自动驾驶的分类，L1~L2级属于辅助驾驶，L3级则是首个由系统主导的等级，被定义为“有条件自动驾驶”，在某些特定场景或环境下，驾驶员无需紧盯路况，可交给车辆自主完成驾驶任务。
+　　记者留意到，此前北京已率先开展L3级路测试点，宝马、奔驰、长安、比亚迪等车企先后获得测试牌照。那么，自动驾驶车出事故“到底谁负责”？《条例》的第三十一条、第三十二条指出：自动驾驶汽车上路通行期间，违反道路交通安全法律法规或者发生交通事故的，由公安交管部门按照国家有关规定调查和处理，相关企业和个人应当配合事故调查处理，并按要求提供相应证据材料。此外，与其他机动车一样，自动驾驶汽车也须遵守现行的交通安全法律法规。
+　　据《法治日报》报道，北京市人大常委会法工委有关负责同志对此解释称，交通事故的责任认定属于国家立法事权，北京地方立法无权作出规定；因此《条例》在这方面与国家规定进行了衔接，要求发生交通事故后由公安交管部门根据国家有关规定调查和处理。
+　　北京君泽君律师事务所孟昕表示，现行法律体系在应对自动驾驶汽车事故责任认定方面面临诸多挑战。目前，我国依然主要依据道路交通安全法和产品质量法对相关事故责任进行划分。这意味着北京率先为L3级的落地开了先河，但在自动驾驶事故责任划分上，仍需要进一步明确。
+　　政策东风催动，L3级落地成车企新目标
+　　今年以来，“高阶智驾”与“智驾平权”已成为车企竞相营销的核心“卖点”。工信部数据显示，2024年具备L2级组合辅助驾驶功能的乘用车新车占比达到57.3%。
+　　《条例》的实施，一定程度上鼓励了国内L3级车辆的加速落地。目前，华为ADS 4.0、小鹏XNGP等系统正加速适配北京路况，目标是年内实现“城市NOA+L3高速脱手”双突破。广汽集团也制定了非常清晰的时间表，今年3月宣布其国内首款L3级自动驾驶乘用车将于第四季度量产上市，并同步推进业内首款L4级前装量产车型下线。据悉，作为国内首批获准L3 级上路试点的车企，广汽已积累超40亿公里L2级智驾里程、4000 万公里L4级Robotaxi运营数据(依托如祺出行、小马智行)。
+　　在近日举办的中国电动汽车百人会论坛(2025)上，工信部副部长辛国斌再度释放出将“有条件批准L3级自动驾驶车型生产准入，推动道路交通安全、保险等法律法规完善”等消息。
+　　中国工程院院士、清华大学智能产业研究院(AIR)院长张亚勤预计，2025年将成为自动驾驶技术突破的关键节点，他甚至预计到2030年，全球约10%的新车将具备L4级能力。
+　　业内分析
+　　L3级驾驶事故车企须担责
+　　“衡量是不是真正的L3，在于出事故后车企敢不敢赔付。”轻舟智航联合创始人、CEO于骞认为，当智驾事故责任从驾驶员转向车企，才是自动驾驶等级跃迁的核心标志。他指出，L3不应是营销口号，无论技术如何冗余、法规如何要求，若车企不敢承诺事故赔付，本质上仍是L2水平。
+　　在中国科学院院士欧阳明高看来，确保大模型“上车”的安全性与可靠性，仍是当前亟待攻克的关键课题。不仅L3级自动驾驶需要尽快解决相关法律法规问题，L4级自动驾驶更需要积累经验循序渐进，目前暂时不宜提出“全民自动驾驶”。从“政策破冰”到取得“全民信任”，自动驾驶的普及注定是一场持久战。
+　　邓莉</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.chinanews.com.cn/gj/2025/04-01/10393105.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>国际</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>现货黄金站上3140美元，黄金概念股持续爆发！能否持续？</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中新经纬4月1日电 1日上午，现货黄金盘中突破3140美元/盎司，续创新高。过去12个交易日内，现货黄金已先后突破3000美元、3100美元两大关口。
+　　数据显示，截至2025年3月收盘，国内外黄金期现价格不断刷新历史高点，COMEX黄金站上3050美元/盎司，沪金主力站上730元/克关口。自2025开年以来，沪金累计涨幅已超17%。
+　　受上述消息影响，4月1日，黄金概念持续爆发。截至发稿，A股市场上，深中华A一度涨停，特力A、湖南白银、曼卡龙、明牌珠宝、萃华珠宝等跟涨。
+中信期货研报指出，市场担忧特朗普或于4月3日推出高达20%的全球关税政策，加剧滞胀风险并打压美元及美债收益率，推动金价创历史新高。
+　　华闻期货认为，避险情绪升温与经济不确定性，叠加美联储降息预期与美元走弱，及央行购金与市场结构性因素，共同推动金价加速上行。
+　　东海期货提到，2025年2月，中国官方黄金储备为7361万盎司，较上月末增加16万盎司。目前，中国央行已连续四个月增持黄金。过去一年，中国官方黄金储备增加142万盎司。对比其他国家央行黄金储备比例，我国国际储备中的黄金储备低于全球平均水平。从优化国际储备结构，推进人民币国际化等角度出发，未来中国央行增持黄金仍是大方向。重点关注各国央行的购金行为对黄金价格的正向拉动，预计来自各国央行的资金有望保持净流入。
+中信期货认为，二季度黄金有望维持多头趋势。长期中仍关注美元信用下行对金价的支撑：美国债务超发的现实难改；逆全球化下的去美元化需求持续，央行购金方向不变，开放险资购买进一步打开机构购金的想象空间，强化市场对黄金的投资信心；长期中美元信用修复的叙事松动。
+　　华闻期货指出，4月关注以下关键变量：(一)美国非农数据。若新增就业人数再次大幅不及预期，可能刺激金价再度加速上涨。(二)美联储货币政策若4月数据(如非农就业、PCE 通胀)疲软，或关税政策导致经济衰退风险升温，美联储可能在5月释放降息信号，甚至在6月直接行动，会强力支撑黄金上涨。(三)美国关税政策。若美国在4月继续升级关税政策，或刺激黄金持仓量进一步激增。(四)央行购金与实物需求。(五)全球局势。(中新经纬APP)
+　　</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.chinanews.com.cn/gj/2025/04-01/10393104.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>创意</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>外卖小哥身陷“算法束缚”等困境怎么破？</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+　　有一群人，每天起早贪黑穿梭于城市大街小巷，他们的工作关乎每个人的吃穿住行。他们伴随互联网新业态而生，被誉为城市运行的“毛细血管”。他们就是新就业群体。
+　　今年国务院《政府工作报告》明确提出“加强灵活就业和新就业形态劳动者权益保障”。全国人大代表、上海市高级人民法院院长贾宇还就此联合部分代表递交了“关于修订劳动合同法的议案”。
+　　上海是我国平台经济的领头羊，近年来以外卖员、快递员、网约车司机等为代表的新就业群体不断扩大。他们不仅为城市高效运行作出贡献，更是成为“平安上海”“法治上海”建设的参与者和见证者。《法治日报》记者近日走进上海的街头巷尾，走进快递站、网约车司机驿站等地，深入了解新就业群体面临的发展困境和上海破解难题、保障其合法权益的探索实践。
+　　去年上海放宽网约车驾驶员户籍限制后，王师傅从陕西来到上海，考取了《网络预约出租汽车驾驶员证》(以下简称“人证”)，又在租车公司租赁了一辆有《网络预约出租汽车运输证》(以下简称“车证”)的营运车，开始了“沪漂”之旅。
+　　“现在一天要开13至14个小时，每月交完车辆租金，到手只有七八千元。”王师傅掰着手指告诉记者，刚来那阵子认为收入尚可，只要自己再辛苦些收入还会增加，可事实上，到一定水平就涨不了了。
+　　“我们还得自己承担保险，一年要缴两万多元，公司虽然推荐了‘众筹保险’，价格便宜一半多，但出了事故很难理赔成功……”他说。
+　　早上7点，徐汇区美罗城外，外卖骑手们拿着各种包装好的早餐鱼贯而出已成为日常。尽管天空飘着细雨，他们却毫不在意。29岁的是一名海归留学生，半年前他绝不会想到自己会成为“外卖小哥”。他笑言自己就是电影《逆行人生》中男主角的现实版。
+　　小杨一开始注册的是众包骑手(无加盟)，由于抢单慢、地理不熟，一天收入仅30元。后来他不得不加盟站点成为专送骑手，接受培训后收入才有所提高。他坦言：“按单计费虽说多劳多得，但我和很多同行都知道，我们的收入还是和算法有关。”
+　　“平台利用算法控制站点配送量，不允许人效(人效=站点总单量/骑手数)超过35单。”一名某外卖平台加盟站站长向记者介绍，以专送骑手每单5元至7元，人均每天跑35单为例计算，即使全勤跑满30天，加上各种奖励费用，一个月到手收入只有七千多元。
+　　“有些专送骑手在熟悉路况和内在窍门后，又会再转行当众包骑手，每单虽然只有3元至4元，但单量不受限制，抢到的也多是不用爬楼的近单。”这名站长说，但是算法就像如来神掌，任凭你会七十二变，却依然被其束缚。
+　　不久前，上海市第二中级人民法院(以下简称上海二中院)审结一起网约车司机交通事故纠纷上诉案。该案司机背后牵连多家公司，所有公司都以自然人服务合作协议、租车协议等为由意欲撇清与司机存在劳动或劳务关系，以逃避事故赔偿责任。
+　　上海二中院经审理认为，平台公司通过网约车平台算法实现对网约车驾驶员的隐蔽控制，实施一定的监督管理，同时对驾驶员缺失“车证”和“人证”存在未履行资质审查义务的过错；而网约车司机当时系加盟商招募从事网约车服务，且平时还对网约车驾驶员进行一定的管理与约束。最终，上海二中院判决平台公司和加盟商对本案交通事故承担相应的赔偿责任。
+　　“去年，上海法院审结新业态劳动争议案件1223件。在司法实践中，上海法院在现有法律框架内努力做好司法保障，破除以连环外包等隐蔽手段规避用人责任的‘障眼法’。”贾宇在递交全国人大议案前，对此做了广泛调研。
+　　他告诉记者：“许多新就业群体在签合同时，甚至不清楚甲方是谁，一旦遇到问题就茫然不知所措。司法保障是最后一道防线，我们有责任也有义务预防和干预其中存在的诉讼风险。”
+　　记者在调查中发现，当前新就业群体权益保障面临三大问题。
+　　一是少数平台为扩大经营对“人证”“车证”缺乏审核。“只要有驾照，再交500元押金就行，上路被查由公司摆平。”采访中一名自称是“上海网约车人事部”的工作人员对此“大包大揽”，甚至还有租赁公司利用修图软件伪造驾龄和车辆性质，让本无资质的司机和车辆进入市场。发生事故时，因“准入造假”被保险公司拒赔，由此产生大量纠纷。
+　　二是合同签订陷阱重重，附加了更多“额外责任”。在司法案例中，有平台与骑手签订自然人服务合作协议，约定“造成任何第三方人身财产损害的，由乙方(骑手)承担全部责任”；还有租车公司与司机签订租车协议时，约定每月必须完成的流水金额和在线时长，完不成要上涨租金。
+　　三是骑手、司机长期处于身体和精神的双重压力，社保覆盖却严重不足。一旦出现问题，很难找到合法合理的救济渠道。
+　　上海市君悦律师事务所主任胡光说，从法律外观主义和终极平台最大获利的经济角度来看，亟须强化平台责任，加强对新就业群体的权益保障，为他们构建一个更加公平合理、合法合规、健康可持续的职业生态。
+　　“我在骑手App上一键报案后，平台第一时间介入，协助完成职业伤害确认、待遇核定等业务办理。”骑手小李在送餐途中因意外骨折，不仅顺利报销了医疗费，还在养伤期间领取了生活保障费，小李享受的正是新就业形态就业人员职业伤害保险(以下简称“新职伤”)。据了解，上海自2022年7月1日起，按照国家统一部署将曹操出行、美团、饿了么等7家平台的就业人员纳入“新职伤”试点范围。
+　　“新就业群体的社保中，最为急需的是工伤保险。”华东政法大学社会法研究所所长李凌云认为，目前试点工作初见成效，可向全行业推广，同时还要匹配相应的商业保险。“新职伤”可以解决医疗、伤残和死亡等相关待遇；商业险则解决财产损失(如车损)以及对第三人造成的人身损害和财产损失。商业险承担主体不宜一刀切，可由司机和平台分别承担；而对于骑手来讲，可实行按单投保。
+　　目前，京东、美团等平台已对外宣布为外卖骑手缴纳社保。京东方面表示，会逐步为全职骑手缴纳五险一金，并承担个人所需缴纳部分；美团方面表示，将制定平衡成本和权益的社保方案，逐步为全职及稳定兼职骑手缴纳社保；有网约车平台推出司机商业养老保障、专属医疗及意外保障、极端天气损失误工保障等举措。
+　　针对算法束缚，李凌云建议，人社部门等应引导平台企业和新就业群体开展协商达成共识，以劳动者的“看法”来优化平台“算法”；对于用工乱象，胡光认为，有关部门应加强对平台的监督治理，尝试建立责任分担机制，严格防范不合理抽成行为和非法用工乱象。
+　　“目前，我国劳动合同法主要针对传统就业方式，难以适应灵活就业的特点和需求，导致灵活就业人员在劳动报酬、劳动时间、社会保障等方面的合法权益保障不到位。”贾宇建议修订劳动合同法，进一步保障灵活就业人员劳动报酬、规范工作时间，进一步明确规范社会保险的缴纳主体、保障范围等，通过专门立法统一规范相关权利义务，保障灵活就业人员的基本权益。
+　　“要解决新就业群体的权益保障问题，需要各方携手，形成共识与合力。”贾宇说，上海作为超大城市，要进一步利用精细化治理的经验优势，持续深化制度创新与实践探索，建立健全灵活就业人员的权益保障机制，力求在重点领域形成关键性突破，为新经济、新业态健康发展注入强劲动力，形成更多可复制可推广的成功经验。
+　　本报记者 余东明 张海燕
+　　本报实习生 张晓颖</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.chinanews.com.cn/chuangyi/2025/04-01/10393103.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>《中华人民共和国境内外国人宗教活动管理规定实施细则》有关问答</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>近日，国家宗教事务局公布了新修订的《中华人民共和国境内外国人宗教活动管理规定实施细则》(以下简称《实施细则》)。《实施细则》公布之际，国家宗教事务局负责人就《实施细则》的修订出台有关问题，回答了记者的提问。
+　　答：修订《实施细则》是规范境内外国人宗教活动的迫切需要。随着中国政府进一步扩大对外开放，境外来华经商、观光旅游、探亲访友的人员数量持续增加，境内外国人参加宗教活动的需求日益增多。原《实施细则》在保障境内外国人正常宗教活动，尤其是参加集体宗教活动方面的规定还需要完善。同时，一些外国人在我国境内进行非法传教、参与非法宗教活动，影响了我国宗教和睦甚至社会和谐稳定。对此，我国宗教界人士、信教群众和一些外籍人员均希望进一步明确相关制度，规范境内外国人宗教活动的管理。
+　　修订《实施细则》是全面推进依法行政的必然要求。按照行政许可法的要求，实施行政许可应当对许可条件、权限、程序、时限等作出具体规定，并向社会公开。原《实施细则》对涉及的4项行政许可：境内外国人集体进行宗教活动临时地点审批、我国五种宗教以外的外国宗教组织及其成员与我国政府部门或宗教界等交往审批、外国人携带用于宗教文化学术交流的宗教用品入境审批、邀请以其他身份入境的外国宗教教职人员讲经讲道审批，需要作进一步规范。因此，有必要通过修订《实施细则》，明确行政许可的相关规定，规范政府宗教事务部门行政许可行为。
+　　答：中国一贯尊重在中国境内的外国人的宗教信仰自由，在1994年《中华人民共和国境内外国人宗教活动管理规定》对此便作出了明确规定。新修订的《实施细则》重申了中国尊重境内外国人的宗教信仰自由，依法保护境内外国人宗教活动。具体而言，境内外国人合法的涉宗教活动主要包括：可以在依法登记的寺院、宫观、清真寺、教堂(以下称寺观教堂)参加宗教活动；可以在寺观教堂或者经批准的临时地点举行集体宗教活动；经所在地宗教团体同意，可以邀请中国宗教教职人员按宗教习惯为其举行洗礼、婚礼、葬礼和道场、法会等宗教仪式；可以与中国宗教团体、宗教院校和宗教活动场所等进行宗教方面的友好往来和文化学术交流活动；外国宗教教职人员经邀请可以在寺观教堂讲经、讲道；经相关宗教团体同意，外国人可以来中国宗教院校留学；经中国宗教院校按照法定程序聘用，外国人可以作为外籍专业人员到宗教院校讲学等。
+　　答：为了做好境内外国人集体宗教活动的服务和管理，《实施细则》规定，境内外国人举行集体宗教活动有两种方式：一是由国内寺观教堂提供专场服务；二是如果寺观教堂不具备提供专场服务条件的，可以在中国政府宗教事务部门批准的临时地点进行。
+　　境内外国人拟在寺观教堂举行集体宗教活动，应当由推选出的召集人向所在地设区的市(地、州、盟)宗教团体提出书面申请。宗教团体根据申请和当地寺观教堂的情况，确定为境内外国人集体宗教活动提供专场服务的寺观教堂。为境内外国人集体宗教活动提供专场服务的寺观教堂应当与召集人签订协议，明确集体宗教活动的时间安排、活动方式、活动次数、活动人数、安全措施、双方权利义务、法律责任等事项。
+　　当地寺观教堂不具备提供专场服务条件的，设区的市(地、州、盟)宗教团体应当书面答复召集人。召集人可以向所在地省级人民政府宗教事务部门申请设立临时地点。省级人民政府宗教事务部门收到申请材料后，应当征求相关县市宗教事务部门以及宗教团体的意见，自受理申请之日起二十个工作日内作出批准或者不予批准的决定。在临时地点参加集体宗教活动的外国人应当遵守中国的法律、法规、规章，不妨碍周围单位和居民正常的生产、学习、生活，接受所在地宗教事务部门的管理。
+　　答：我们注意到，确有一些外国人不遵守我国法律法规，在我国境内举行非法宗教活动、违法进行传教活动。《实施细则》明确规定，境内外国人进行宗教活动，应当遵守中国的法律、法规、规章，尊重中国宗教独立自主自办原则，接受中国政府依法管理；不得利用宗教损害中国国家利益、社会公共利益和公民合法权益，不得违背中国的公序良俗。境内外国人不得进行下列涉宗教的活动：(一)干涉和支配中国宗教团体、宗教院校、宗教活动场所的事务，干涉宗教教职人员的认定和管理；(二)成立宗教组织，设立宗教办事机构、宗教活动场所或者宗教院校；(三)宣扬宗教极端思想，支持、资助宗教极端主义和非法宗教活动，利用宗教破坏中国国家统一、民族团结、宗教和睦与社会稳定；(四)擅自开展讲经、讲道或者举行集体宗教活动；(五)在中国公民中发展宗教教徒，委任宗教教职人员；(六)利用宗教进行妨碍中国司法、教育、婚姻、社会管理等制度实施的活动；(七)制作或者销售宗教书刊、宗教音像制品、宗教电子出版物等宗教用品，散发宗教宣传品；(八)接受中国组织及公民宗教性的捐赠；(九)组织开展宗教教育培训；(十)利用互联网进行非法宗教活动；(十一)其他涉宗教的违法活动。</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.chinanews.com.cn/sh/shipin/cns/2025/04-01/news1017349.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江南华南阴雨暂歇有望放晴 中东部温暖回归多地重返20℃ </t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>中国天气网讯 进入四月第一天，我国大部地区将继续回暖，北方多地最高气温重回20℃以上，江南、华南多地阴雨天气暂时停歇，也将加入升温行列，但西南地区降雨频繁气温回升缓慢，多地最高气温在15℃上下。预计清明假期期间，中东部大部暖意在线，湖北、河南等地或冲击30℃，但昼夜温差较大，公众早晚时段仍需保暖防着凉。
+　　今起至清明假期，我国气温整体有所回升，其中今明两天，升温的主力区域将集中在降水消退后的南方地区，江淮、江汉、江南、华南的累计升幅普遍可达10℃左右、局地15℃左右，回暖非常迅速。升温后，从华北东部至江南北部和西部、华南西部、云南中西部最高气温都将在20℃或以上。
+　　不过在降水频繁的西南地区，气温回升较为缓慢。大城市中，重庆、贵阳本周多数时间气温都处在偏低状态，贵阳今明天最高气温仅有14℃，天气阴冷，需持续做好保暖工作。
+　　预计清明假期期间，中东部将有成片20℃以上的温暖，华北到江南、华南中东部一带最高气温可达25℃左右，河南、湖北等地甚至将冲击30℃。其中，郑州明天气温短暂下滑，后天起至清明假期将一路升温，4月6日最高气温或可达31℃。各地白天暖意不断升级，但最低气温回升缓慢，昼夜温差可超10℃，公众早晚时段出行需注意添衣防感冒。
+　　今起三天，我国降水范围将逐渐缩减，持续阴雨的江南、华南多地有望放晴，阳光逐渐上线。其中今天，新疆沿天山地区和伊犁河谷高海拔地区、青海南部、西藏东部、川西高原、内蒙古东部、河北北部、黑龙江中部、吉林中东部等地部分地区有小雪或雨夹雪，其中，新疆伊犁河谷高海拔地区、西藏东北部、青海东南部、川西高原北部等地部分地区有中到大雪，西藏东北部、川西高原北部等地局地有暴雪。新疆北疆北部、西藏东南部、四川盆地西部和中部、重庆南部、贵州西部、云南南部和东北部、内蒙古东部、辽宁南部和东部、吉林西部、黑龙江中部和东北部、海南岛南部、台湾岛等地部分地区有小到中雨。
+　　明天，新疆北疆东部和沿天山地区以及伊犁河谷高海拔地区、西藏东部、川西高原中部等地部分地区有小到中雪或雨夹雪，其中，西藏东部局地有大雪。新疆北疆中东部、西藏东南部、四川盆地西部、甘肃西南部、东北地区东部、台湾岛中东部等地部分地区有小到中雨。
+　　近期，西北地区东部、华北等地雨雪稀少，森林火险气象等级较高，临近清明，大家需注意用火安全，尽量避免在户外使用明火，如遇火情及时报警。清明假期，南方雨水将再度发展，公众需关注临近天气预报，合理安排出行计划。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.chinanews.com.cn/sh/shipin/cns-d/2025/04-01/news1017348.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>财经</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>“智慧基因”带飞生产效率，挑战也随之而来</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+　　自从2025年初火到现在，DeepSeek在各行各业的应用已经取得了不少成果。作为新一代人工智能技术的领头羊，DeepSeek正在深刻地改变着传统企业与行业的运营模式和发展轨迹。这项技术利用深度学习算法和大数据分析，为企业决策提供精准支持，推动传统产业向智能化方向转型。在制造业、零售业、金融服务业等多个领域，DeepSeek的应用正在重塑行业格局，在提升效率和优化成本的同时，也催生出新的商业模式和增长点。
+　　近日，在中铁资源鹿鸣矿业公司法律合规部办公室，法务专员聂明月将新拟定的43页的设备购买合同上传至“钼光大模型”。30秒后，法律助手不仅标出3处存在歧义的条款，还自动给出决策建议。
+　　“原本需要三四天完成的合同审查，如今不到半小时即可完成，而且关键条款漏检率归零”。该公司法律合规部部长赵春蕾说，目前该系统已协助审核合同13份，规避潜在法律风险43项，合同流转效率提升300%。自从完成DeepSeek等国产大模型本地化部署和试运行智能矿山AI服务平台“钼光大模型”后，中铁资源鹿鸣矿业公司总经理孟庆胤认为，“我们将见证矿业认知革命的真正爆发！”
+　　“DeepSeek为道岔制造注入‘智慧基因’，实用性很强。”最近，中铁宝桥南京公司的信息化团队成功将DeepSeek-R1模型和千问大模型Qwen2.5接入ERP系统，开发了道岔智能助手。这个智能化制造新体系实现了订单管理、工艺执行、质量管控的全流程数字化升级。
+　　“钼光大模型”“道岔智能助手”只是企业接入DeepSeek进行数字化升级的一个缩影。
+　　在实际应用中，DeepSeek的应用成效显而易见。制造企业引入DeepSeek系统后，通过实时监控生产线运行状态，可预测设备故障，优化生产调度，提升整体生产效率。
+　　而零售行业应用DeepSeek的消费者行为分析系统后，实现了精准的商品推荐和库存管理。系统通过分析顾客购买记录、消费习惯等数据，为每家门店提供个性化的商品组合建议，较大地提高了库存周转率，减少了滞销。
+　　在金融服务业，DeepSeek也在悄然介入。据中国工商银行消息，近期工商银行在同业率先完成DeepSeek最新开源大模型的私有化部署，并将其接入行内“工银智涌”大模型矩阵体系，推动金融业务场景的智能化升级。据悉，工商银行聚焦金融大模型行业应用，按照“全栈自主可控、全面技术突破、全域场景赋能、全辖安全防护”的目标，构建集算力、算法、数据、工具、安全、应用、生态于一体的“工银智涌”企业级金融大模型技术应用体系，形成以大模型为核心的新一代金融业务赋能模式，打造“人工智能+金融”行业新质生产力。
+　　据报道，浙江大学医学院附属第二医院胸外科主任医师接诊时，DeepSeek仅用56秒就完成精准诊断，结论和临床团队高度吻合，还能纠正医生提问的模糊描述，事件在医疗界引起广泛关注。据不完全统计，目前国内已有超百家医院接入DeepSeek。北京友谊医院、北京清华长庚医院、北京大学第三医院等多家医院纷纷宣布完成本地化部署。
+　　如今，流行“遇事不决问DeepSeek”，有网友表示，“DeepSeek治好了我的情绪病”。在互联网分享“被AI感动哭”“DeepSeek的情绪价值拉满了”的帖子比比皆是，甚至有网友认为，DeepSeek比心理医生更适合自己。
+　　可以看出，DeepSeek正在为医疗行业带来前所未有的变革。广义来看，从疾病诊断到药物研发，从患者管理到医疗资源优化，DeepSeek的技术正在全方位赋能医疗行业。在智能影像诊断方面，可以大幅提升诊断效率与准确性，其AI系统能够快速识别医学影像中的病变区域，辅助医生进行诊断。而在治疗方面，DeepSeek可以推出个性化治疗方案，给病人提供情绪价值，更有助病人恢复健康。
+　　同样，DeepSeek对教育行业的影响也颇受瞩目。个性化教育方式、智能教学、优化教育资源等等，DeepSeek通过其创新的技术解决方案，正在推动教育模式转型和升级。
+　　有教育界人士认为，DeepSeek的出现和广泛应用，对未来选择学习专业和方向有较大影响，比如“大学能否培养出能够应用AI从事未来的研究和工作的新型人才”“就业时更看重求职者应用AI的实际能力”。
+　　DeepSeek通过其创新的AI技术，正在为医疗和教育行业带来深刻的变革。其在智能影像诊断、个性化学习等领域的技术突破，不仅提升了行业效率，还改善了服务质量。然而，在技术应用的过程中，DeepSeek也面临着数据隐私、技术透明性和人文平衡等挑战。
+　　对此，上海市数据科学重点实验室主任肖仰华表示担心，在智能教学过程中，或许会被AI抓取教师、学生的个人隐私。肖仰华认为，比这些问题更可怕的，是AI的大规模滥用和误用，可能会削弱学生独立思考的能力。
+　　看来，DeepSeek能否在技术创新与行业需求之间找到平衡，将成为其持续赋能医疗和教育行业的关键。
+　　尽管DeepSeek带来了诸多机遇，但其应用也面临着数据安全、算法偏见等挑战。企业需要建立完善的数据治理体系，确保数据使用的合规性和安全性。同时，算法模型的透明性和公平性也需要持续改进，以避免决策偏差。
+　　人才短缺是另一个亟待解决的问题。DeepSeek的应用需要既懂业务又懂技术的复合型人才，这类人才的培养需要时间和投入。企业需要建立完善的人才培养机制，通过内部培训和外部引进相结合的方式，打造适应智能化转型的人才队伍。
+　　展望未来，DeepSeek与传统产业的融合将更加深入。随着技术的不断进步和应用场景的拓展，DeepSeek有望在更多领域发挥其价值。企业需要保持开放和创新的态度，积极探索DeepSeek的应用场景，在数字化转型中把握先机。
+　　在技术快速迭代的时代，传统企业和行业正站在转型升级的关键节点。以DeepSeek为代表的人工智能技术，既是挑战也是机遇。只有主动拥抱变革，积极推动技术与业务的深度融合，传统企业才能在数字化浪潮中实现跨越式发展，开创新的增长空间。
+　　值得注意的是，DeepSeek的应用效果因行业和企业特点而有所差异。专家建议，企业在引入DeepSeek时，需要结合自身实际情况，制定合理的实施策略。同时，政府相关部门也在积极制定行业标准和应用指南，为DeepSeek的健康发展提供政策支持。
+　　本报记者 徐潇《工人日报》(2025年04月01日 07版)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.chinanews.com.cn/cj/2025/04-01/10393089.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>财经</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>公共场所摄像头须设置显著提示标识</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+　　编者按：公共安全视频系统管理单位应当合理确定图像采集设备的安装位置、角度和采集范围，并设置显著的提示标识；细化完善公平竞争审查总体要求、审查标准；集中用餐单位应当依法加强对单位食堂、承包经营企业、供餐单位经营行为的管理……4月起，《公共安全视频图像信息系统管理条例》《公平竞争审查条例实施办法》《集中用餐单位落实食品安全主体责任监督管理规定》等一批新规施行，聚焦群众关切，以法治力量推动经济社会高质量发展。
+　　近些年，公共场所视频图像信息被随意收集、泄露、滥用等问题时有发生，公共安全视频系统到底谁能建、怎么建、谁来管等一系列问题，一直是社会关注的焦点。
+　　公安部相关负责人介绍，公共场所的视频图像信息系统在打击违法犯罪、加强治安防控、处置突发事件、优化城市管理等领域发挥了重要作用。但同时，在公共场所安装图像采集设备缺少有效监管，随意收集使用视频图像信息问题突出，不少地方仍然存在统筹规划不到位、部门职责不清晰、安装设置不规范等问题，个别地方甚至出现使用单位及其工作人员非法对外公开、提供视频图像信息导致个人隐私、个人信息泄露的情况，造成恶劣社会影响。
+　　为进一步规范公共安全视频图像信息系统管理，维护公共安全，保护个人隐私和个人信息权益，国务院制定《公共安全视频图像信息系统管理条例》(以下简称《条例》)，自4月1日起施行。
+　　“网络安全法、数据安全法、个人信息保护法等法律施行后，对网络安全、数据安全和个人信息处理活动进行了全面规范。本次出台的《条例》在上位法基础上，对公共场所视频图像信息收集、存储、使用、加工、传输、提供、公开、删除等环节中遇到的各类问题进一步明确。”北京大学法学院副院长车浩教授表示。
+　　很多人关心，街面拍到的个人信息会不会被滥用？中国人民公安大学侦查学院刘为军教授表示，对公民个人隐私和个人信息权益采取强保护态度，是《条例》的主要亮点之一。根据《条例》规定，公共安全视频系统管理单位使用视频图像信息，应当依法保护个人隐私和个人信息，不得滥用、泄露。如需依法公开传播视频时，需对人脸、车牌等敏感信息做模糊处理，防止“人肉搜索”等二次伤害。
+　　为了充分考虑特殊地点的隐私保护，《条例》明确了禁止安装图像采集设备的场所，同时对图像采集设备的建设主体、建设目的、安装位置角度等都作出严格限定。比如，《条例》禁止在旅馆、民宿等经营接待食宿场所的客房或者包间内部，学生宿舍或者单位为内部人员提供休息服务的房间内部，公共的浴室、更衣室等内部，以及安装后能够拍摄、窥视、窃听他人隐私的其他区域、部位安装图像采集设备设施，并明确上述经营管理单位或个人的日常管理和检查义务。
+　　刘为军表示，《条例》实施后，将公共图像采集设备的画面信号放到网上直播，或者未经他人允许将采集内容发到网络上等行为，都将受到更加严格的法律规范。
+　　为了降低视频图像信息被泄露的风险，《条例》明确规定视频图像信息保存期达到30日后，对已经实现处理目的的视频图像信息，应当予以删除，法律、行政法规另有规定的除外。如国家机关为履行法定职责确实需要查阅、调取视频图像信息，《条例》规定应当依照法定权限、程序，严格遵守保密规定，不得超出履行法定职责所必需的范围和限度。
+　　《条例》实施后，还能在家门口安装摄像头吗？这种行为会涉嫌违法吗？《条例》规定，在非公共场所安装图像采集设备及相关设施，不得危害公共安全或者侵犯他人的合法权益，对收集到的涉及公共安全、个人隐私和个人信息的视频图像信息，不得非法对外提供或者公开传播。
+　　“家门口通常不是《条例》规定的公共场所，个人出于自身安防需要，可以在家门口安装摄像头，但不能危害公共安全和他人合法权益，所收集到的涉及公共安全、个人隐私和个人信息的视频图像信息，不得非法对外提供或者公开传播。对于确需认定为公共场所的家门口，只能出于公共安全需要安装图像采集设备，且仅能由对该场所负有安全管理义务的主体安装。”刘为军说，考虑到非公共场所安装使用图像采集设备不可避免会采集到涉及公共场所的视频图像，可能会侵犯他人合法权益甚至危害公共安全、国家安全，《条例》遵循最小介入原则，从使用角度作出必要限制。
+　　另外，《条例》对老百姓能不能查看图像采集设备的问题作出了专门回应，这一行为有了法律依据。车浩介绍，根据《条例》，个人未经授权不得随意查看或传播图像采集设备内容，普通民众因生命财产安全需要查阅时，需经管理单位同意，且不得非法对外公开。个人若因老人、儿童走失等紧急情况申请查阅，需经管理单位同意并保护隐私。
+　　老百姓如何监督身边的违规图像采集设备？发现后该如何举报？刘为军介绍，《条例》实施后，公共场所的图像采集设备就必须设置显著的提示标识，对于每一个公民来讲，最简单的判断方式就是图像采集设备有无显著的提示标识。发现疑似违法的图像采集设备的，可以向属地公安机关举报，公安机关将会开展核查。
+　　《公平竞争审查条例实施办法》将于4月20日起施行
+　　细化审查标准  维护公平竞争市场秩序
+　　本报北京3月31日电  (记者林丽鹂)为深入贯彻落实《公平竞争审查条例》(以下简称《条例》)，加强公平竞争审查刚性约束，维护公平竞争市场秩序，加快推进全国统一大市场建设，市场监管总局近日发布《公平竞争审查条例实施办法》(以下简称《办法》)，将于4月20日起正式施行。
+　　《办法》共48条，在《条例》框架下，细化完善了公平竞争审查总体要求、部门职责、审查标准、审查机制、审查程序等。
+　　《办法》细化审查标准，将《条例》规定的限制或者变相限制市场准入和退出、限制商品要素自由流动、影响生产经营成本、影响生产经营行为等四个方面的审查标准细化为66项具体情形，同时明确例外规定中“没有对公平竞争影响更小的替代方案”“合理实施期限”等概念的含义，防止例外规定被滥用，损害市场竞争。同时健全审查机制，对起草单位开展公平竞争审查的程序和内容提出具体要求，明确听取利害关系人意见的方式和范围等；细化由市场监管部门会同起草单位开展公平竞争审查的政策措施范围和工作程序。
+　　《数字文化馆资源和技术基本要求》自4月1日起实施
+　　统一建设标准  推动数字文化资源共享
+　　本报北京3月31日电  (记者郑海鸥)国家标准《数字文化馆资源和技术基本要求》自4月1日起实施。该标准是文化馆领域数字化方面的首个国家标准，是对我国近10年来文化馆数字化建设的规范化总结与标准化提升。
+　　文化和旅游部全国公共文化发展中心相关负责人介绍，我国多地在数字文化馆建设方面进行了实践探索，积累了一定经验，但在开展工作中也面临瓶颈，比如缺少资源和技术的基本要求，数字资源的分类、版权、建设、共享和技术平台的运行保障、数据采集等方面缺少参照的标准，等等。“‘数字文化馆’这一概念及其内涵、主要构成、基本原则等首次在国家标准中得以明确和规定。”该负责人说。
+　　《数字文化馆资源和技术基本要求》规定了数字文化馆建设与服务中数字资源、技术平台、数据管理方面的基本要求，便于各地在建设数字文化馆的过程中统一建设标准，进而实现数字文化资源的共建共享。同时，结合各地数字文化馆平台与国家公共文化云对接过程中的实际需要，在标准中明确了数据字段，为数字文化馆建设提供线上线下数字服务的基本框架。
+　　本报记者 张天培
+　　《人民日报》(2025年04月01日 第 10 版)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.chinanews.com.cn/cj/2025/04-01/10393096.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>文化</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>自家门口装摄像头侵权吗？法官释法</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>您是否曾在走廊遇到被邻居家摄像头“凝视”的尴尬？当智能门铃成为千家万户的“门神”，它们的“眼睛”该望向哪里？4月1日，我国首部系统性规范公共安全视频管理的行政法规正式施行，《公共安全视频图像信息系统管理条例》对公共安全视频系统建设、使用进行全面规范，明确划定了公共场所摄像头的安装范围、备案制度及安装禁区。其中，更是首次为家门口安装的摄像头、智能可视门锁等设备划定“行为红线”。那么，在自己家门口到底能不能安装摄像头？怎么安装不违规？已经安装了的怎么办？
+　　在很多人看来，我在自己家门口装摄像头本就属于个人行为，为什么会专门写进法律条例？我们先来看看条例当中是如何规定的。
+　　条例明确：在非公共场所安装图像采集设备设施不得危害公共安全或者侵犯他人合法权益，不得非法对外提供或者公开传播涉及公共安全、个人隐私和个人信息的视频图像信息。
+　　中国人民公安大学侦查学院教授 刘为军：根据条例规定，公民基于自身的安全防范的需要，在自己家安装这种图像采集设备是不违规的。但是我们要注意到，我们安装摄像头，并不仅仅是我自己的一个保障，也可能会影响到其他人的权益。所以如果说你的图像采集设备会采集到公共场所的信息，那么对于公共场所信息的使用，那么必须遵守这个条例的规定，你也不能够非法使用，不能够对外提供和非法传播。
+　　如果摄像头拍到了邻居的私人空间，会侵犯邻居的隐私权吗？邻居有权要求拆除吗？27岁的小丽独自居住在长沙某小区的高层住宅楼。因为生活垃圾的堆放问题，和邻居产生过争执。出于独居的自身安全问题考虑，小丽在自家的入户门上安装了智能可视门铃，然而不久之后却被邻居告上了法庭。近日，湖南长沙雨花区人民法院就审理了这起因在家门口安装摄像头引发的邻里纠纷。
+　　然而，问题就出在这款可视门铃的拍摄范围，房屋所在楼层为两梯三户结构，小丽处于中间户，可视门铃的摄录范围对准了公共电梯井的出入口，门前人员移动或停留都将触发自动拍照录像，所记录的视频、图片等内容将推送到小丽的手机之上。而小丽在安装摄像头前未征得相关邻居们的同意。
+　　可视门铃拍摄的位置覆盖刘先生一家出门必经的楼道。因此，刘先生认为，小丽安装的可视门铃侵犯到了他的行踪隐私，要求拆除。
+　　2024年底，刘先生将小丽起诉至法院，要求拆除可视门铃，并赔偿精神损失、误工损失共计8万元。
+　　本案的争议焦点集中在公民隐私权与公民安全保障权利之间的冲突。
+　　湖南省长沙市雨花区人民法院民事审判一庭庭长 张松杰：我有一些不愿被别人知道的行为、信息、空间，我有保护这些信息不被别人知晓窥探的权利，这就是隐私权。对于被告而言，每个公民的生活安全保障权利也是法定的，也是要有法律保护的。
+　　长沙市雨花区人民法院审理认为，原告的家庭内部活动线索、出入行踪信息，乃至家庭社会交往情况均属个人隐私，依法受法律保护。而被告出于“生活安全保障”的需求，虽有安装摄像头的权利，但行使权利时超出了合理范围，侵犯了其他公民的隐私权。
+　　最终，法院判决被告拆除安装在入户门前的可视门铃，驳回原告的其他诉讼请求。
+　　湖南省长沙市雨花区人民法院民事审判一庭庭长 张松杰：原告面对被告的摄像头，他每一天的行程，出门的时间、日期、所见的朋友，社交活动，都已经被被告掌握了，就已经超出了被告的安全保障权利。精神抚慰金这块，我们就考虑到原告他目前没有举证证明他精神损害具体的程度，以及由此产生的具体的损失数额，所以对这一块我们就没有支持。
+　　在实际生活中，对于已经在家门口安装了摄像头的朋友们来说，如何找到邻里双方都能接受的解决方案呢，来看江苏无锡法院审理的案例。
+　　家住无锡某小区的戴先生，因邻居在自己门口安装摄像头，认为摄像头侵犯了他们的隐私权，要求拆除，但邻居仅仅将摄像头移了个位置。因协商不成，戴先生将邻居告上法庭。
+　　无锡市新吴区人民法院江溪法庭法官 陈莹：原先的摄像头，是安装在入户门的正上方，就是我们现在看到目前还有三个孔的地方。摄像头可以360°旋转，这个方位是原告家的卧室，摄像头必然能够拍摄到原告家卧室的情况。同时这个方位是原告家厨房，摄像头安装之后，肯定能够拍到原告家中厨房的相关活动信息。后来被告就将原先正上方的摄像头，移位到了我们现在看到的右手边悬梁处，安装在了这个地方，但是移位后的摄像头依然可以360°旋转，还是同样可以拍摄到原告家卧室的情况。
+　　法院认为，原告戴先生夫妇进出家门及在住宅内的活动信息，与人身和财产安全、私人生活习惯等高度关联，应视为具有隐私性质的人格权益，应当受法律保护。在法院的调解下，被告主动进行了整改，给摄像头加装了挡板。
+　　无锡市新吴区人民法院江溪法庭法官 陈莹：被告安装挡板后的摄像头，已经无法拍摄到原告进出家门的活动信息，在这种被告已经没有实际侵犯事实的情况下，最终我们没有判决支持原告的诉请，驳回了原告要求被告拆除摄像头的诉求。
+　　从法院的判决可以看出，自家门口安装的摄像头一旦“越界”，就可能侵犯到他人的隐私权，个人在家门口安装摄像头时，怎么安装才合法合规呢？
+　　个人在家门口安装摄像头，需要注意以下三点。
+　　安装前，提前沟通：最好征得邻居的同意或进行善意提醒，避免误会和矛盾。
+　　安装时，注意角度：要精心选择摄像头安装位置，并调整拍摄角度，可以通过在摄像头周边安装挡板等方式，确保拍摄范围只覆盖自家门口必要区域，避免涉及邻居住宅内部、窗户、仅供邻居通行的通道等私人空间，同时，尽量关闭自动追踪、录音等功能。
+　　安装后，严管数据：对摄像头拍摄存储的视频图像信息，严格保密，防止信息泄露，不得非法对外提供和公开传播。
+　　湖南省长沙市雨花区人民法院民事审判一庭庭长 张松杰：比如说邻居，比如说另外一户，要主动跟他们沟通，征得他们的同意，否则的话，在没有征得公共区域相关利害关系人同意的情况下就贸然装摄像头，而且它的角度已经覆盖了公共区域参与人员的行程轨迹，这就涉及了侵权。
+　　如果邻居，也就是公共区域的相关利害关系人，不同意你在家门口安装摄像头，又该怎么办呢？
+　　湖南省长沙市雨花区人民法院民事审判一庭庭长 张松杰：如果对方不同意的情况下，调整摄像头安装的位置，使这个摄像头尽量只采集到我们自己家人的出行信息。比如说录音的功能，晚上夜间红外线的功能尽量关闭。不能侵害到相关利害关系人的隐私信息，包括出行、会客、时间、日期、声音等等，我认为边界判断的原则在这里，不能侵犯到采集到他人的隐私信息即可。
+　　法官提示，安装摄像头的业主需要留存摄像头覆盖区域示意图及调整记录，以证明安装时已规避他人隐私。
+　　湖南省长沙市雨花区人民法院民事审判一庭庭长 张松杰：装的时候尽到了相关的义务，安装的时候我是怎么考虑的，这个角度怎么调整的，功能有哪些，然后录像的范围是不是涉及了其他人的公共区域、出行信息。把这些证据保存好，如果说起了纠纷，这个我们可以自证，我们安装的时候已经考虑到了对邻居相关隐私权的保护，我们没有侵权，我们可以举证证明。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.chinanews.com.cn/cul/2025/04-01/10393091.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>财经</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>来自4.8亿年前 科学家发现迄今为止最古老的层孔海绵化石</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>层孔海绵是奥陶纪-泥盆纪(古生代)标志性的浅海造礁动物之一，在礁构建中的作用、生态地位和地理分布上类似于现代珊瑚。在中奥陶世达瑞威尔晚期(距今4.6亿年前)，层孔海绵几乎同时融入热带至亚热带气候区的全球礁生态系统。因为受到奥陶纪生物大辐射事件期间海洋生物多样化的影响，这一时期的礁生态系统从微生物主导向层孔海绵和珊瑚主导转变。然而，层孔海绵突然融入礁生态系统引发一系列有趣的关键科学问题：最早的层孔海绵何时出现？它们是如何获得矿化骨骼的？最早的层孔海绵在古生态中扮演了什么角色？它们如何成为礁生态系统的重要组成部分？一系列问题因为缺少早期层孔海绵的化石记录而无从得知。
+　　近日，中国科学院南京地质古生物研究所早古生代研究团队与韩国古生物研究团队等专家在宜昌远安发现了迄今为止最古老的层孔海绵化石(距今4.8亿年前)，名为嫘(léi)祖冠毛层孔海绵。这一发现不仅将造礁的层孔海绵的化石记录提前了约2000万年，还揭示了早期礁生态系统和生物矿化演化的独特机制。该成果于北京时间4月1日在《美国国家科学院院刊》(PNAS)发表。
+　　通过研究，科研人员发现嫘祖冠毛层孔海绵是通过氟磷灰石构建其骨骼的，这在整个海绵类中从未见过。这一新发现确立了多孔动物门，这是第一个已知的利用三种主要生物矿物质(硅、碳酸钙和磷酸钙)的后生动物门。早期层孔海绵骨骼中磷酸盐的存在拓展了人类对早期动物生物矿化能力的理解，这表明早期海绵可能已具备多样化生物矿化策略所需的遗传能力。
+　　不仅如此，嫘祖冠毛层孔海绵还形成复杂的礁结构，在框架构建和结合其他造礁生物组分(如钙微生物、石松海绵、瓶筐石、棘皮动物等)方面发挥了关键作用。这些早期的层孔海绵所建造的礁结构的复杂性堪比后来的礁生态系统。这一发现将造礁层孔海绵的化石记录提前了约2000万年。
+　　这项研究不仅在于填补了层孔海绵早期演化历史的空白，还为理解早期动物的生物矿化过程提供了新的视角，揭示了地球历史上关键时期礁生态系统的复杂性，以及生物如何适应和改变环境，推进了我们对早期生命演化的理解，还为未来研究早期地球环境与生物相互作用提供了新的方向。它展示了生物多样性和生态系统复杂性在地球历史早期阶段(距今4.8亿年前)就已经存在，为我们理解现代海洋生态系统的起源和演化提供了宝贵的线索。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.chinanews.com.cn/cj/2025/04-01/10393099.shtml</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>